--- a/data/target_ffr.xlsx
+++ b/data/target_ffr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albert/Documents/1_Economics/Research/UMP/Empirical Part/Generate Shocks/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albert/Dropbox/0_Research/Active/UMP/Empirical Part/Generate MP Shocks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434D0CC2-C693-134D-B179-0FC3E3902E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DE771C-50B5-6545-96A0-14ED4E150037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{76090649-06DA-D042-ADBD-12774B4C4F40}"/>
+    <workbookView xWindow="30240" yWindow="-18920" windowWidth="19220" windowHeight="21000" xr2:uid="{76090649-06DA-D042-ADBD-12774B4C4F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="467">
   <si>
     <t>MTGDATE</t>
   </si>
@@ -1389,6 +1389,54 @@
   </si>
   <si>
     <t>Rate_change</t>
+  </si>
+  <si>
+    <t>2019-01-30</t>
+  </si>
+  <si>
+    <t>2019-03-20</t>
+  </si>
+  <si>
+    <t>2019-05-01</t>
+  </si>
+  <si>
+    <t>2019-07-31</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2020-01-29</t>
+  </si>
+  <si>
+    <t>2020-03-15</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-06-10</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-09-16</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
   </si>
 </sst>
 </file>
@@ -1768,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCCF096-117B-C64E-A851-E7EEF55DBC40}">
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D473"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -6718,6 +6766,209 @@
         <v>2.125</v>
       </c>
     </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A450" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B450" s="3">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A451" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B451" s="3">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A452" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B452" s="3">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A453" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B453" s="3">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A454" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B454" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="C454">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A455" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B455" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="C455">
+        <v>2.125</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A456" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B456" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="C456">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A457" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B457" s="3">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <f>(1.5+1.75)/2</f>
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A458" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B458" s="3">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <f>(1.5+1.75)/2</f>
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A459" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B459" s="3">
+        <v>-1.5</v>
+      </c>
+      <c r="C459">
+        <f>(1.5+1.75)/2</f>
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A460" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B460" s="3">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A461" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B461" s="3">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A462" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B462" s="3">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A463" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B463" s="3">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A464" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B464" s="3">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A465" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B465" s="3">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A466" s="2"/>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A467" s="2"/>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A468" s="2"/>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A469" s="2"/>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A470" s="2"/>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A471" s="2"/>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A472" s="2"/>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A473" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
